--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -15,6 +15,14 @@
     <sheet name="ConstrainedPickupDist_1c" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ConstrainedGoToOpen_1c" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ConstrainedGoToObjDoor_2c" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ConstrainedActionObjDoor_2c" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ConstrainedGoToLocal_2c" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ConstrainedOpenDoor_2c" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ConstrainedGoToOpen_2c" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ConstrainedPickupDist_2c" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ConstrainedOpenDoorsOrder_2c" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConstrainedOpenDoorLoc_2c" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1519,6 +1527,3258 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Constraint Adapter Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>510.74 ± 425.87</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8.47 ± 11.16</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>588.56 ± 430.30</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>28.71 ± 32.57</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>523.26 ± 436.23</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10.09 ± 12.71</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>590.95 ± 423.72</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>23.52 ± 30.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>510.74 ± 425.87</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>8.47 ± 11.16</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>588.56 ± 430.30</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>28.71 ± 32.57</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>523.26 ± 436.23</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>10.09 ± 12.71</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>590.95 ± 423.72</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>23.52 ± 30.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Constraint Adapter Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>127.90 ± 130.66</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>127.54 ± 114.48</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>23.67 ± 34.31</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>130.36 ± 129.39</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.79 ± 10.34</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>116.53 ± 113.54</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>19.46 ± 28.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>146.64 ± 133.89</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.35 ± 3.38</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>142.24 ± 119.67</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>31.18 ± 41.63</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>144.25 ± 133.43</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.65 ± 12.57</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>126.73 ± 111.84</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>17.79 ± 26.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>137.93 ± 127.34</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>121.60 ± 109.19</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18.10 ± 23.26</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>139.26 ± 123.99</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.32 ± 1.19</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>116.11 ± 112.26</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>16.46 ± 22.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>122.10 ± 125.78</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.13 ± 1.02</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>146.05 ± 116.46</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>21.50 ± 29.66</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>125.56 ± 126.87</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.25 ± 1.16</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>148.41 ± 120.45</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>18.34 ± 24.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>132.19 ± 118.63</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>155.66 ± 115.50</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>18.29 ± 21.27</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>145.00 ± 121.70</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.46</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>140.09 ± 111.16</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>14.90 ± 17.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>136.27 ± 119.37</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>150.03 ± 110.65</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18.14 ± 23.37</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>182.39 ± 124.42</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.27 ± 2.19</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>154.29 ± 118.45</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>15.48 ± 21.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>133.84 ± 126.31</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>0.10 ± 1.46</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>140.52 ± 115.02</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>21.81 ± 30.17</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>144.47 ± 128.02</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>0.73 ± 6.78</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>133.69 ± 115.64</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>17.07 ± 23.73</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Constraint Adapter Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>632.25 ± 309.98</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7.43 ± 15.70</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>516.68 ± 338.78</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>33.70 ± 42.31</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>636.23 ± 311.64</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>13.17 ± 28.73</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>545.10 ± 334.52</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>28.93 ± 35.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>518.00 ± 363.36</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12.10 ± 23.19</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>618.43 ± 295.64</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>27.23 ± 34.30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>475.02 ± 374.44</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>18.70 ± 37.65</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>519.57 ± 330.41</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>36.37 ± 48.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>539.75 ± 356.25</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>18.32 ± 37.53</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>602.98 ± 301.90</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30.32 ± 33.65</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>559.93 ± 344.91</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>19.33 ± 35.10</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>626.95 ± 285.94</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>27.28 ± 44.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>669.77 ± 280.58</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>17.92 ± 35.33</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>615.47 ± 289.74</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>31.00 ± 50.76</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>707.28 ± 233.75</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>15.73 ± 36.55</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>633.50 ± 269.34</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>17.70 ± 29.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>572.80 ± 334.86</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>14.87 ± 44.47</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>578.00 ± 312.83</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>27.02 ± 49.25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>613.75 ± 317.84</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>8.00 ± 25.40</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>606.83 ± 284.82</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>14.33 ± 20.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>586.51 ± 335.26</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>14.13 ± 33.17</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>586.31 ± 310.55</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>29.85 ± 42.74</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>598.44 ± 329.29</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>14.99 ± 33.29</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>586.39 ± 305.60</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>24.92 ± 37.96</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Constraint Adapter Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>429.57 ± 417.96</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>19.03 ± 47.71</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>366.07 ± 356.59</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>23.37 ± 52.67</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>403.73 ± 412.95</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>17.60 ± 36.36</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>455.83 ± 417.09</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>28.97 ± 56.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>424.41 ± 417.36</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20.29 ± 90.30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>482.92 ± 422.05</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>31.04 ± 76.39</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>422.32 ± 403.95</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>29.40 ± 94.35</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>437.91 ± 397.43</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>18.32 ± 39.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>487.24 ± 398.64</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>21.26 ± 66.86</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>539.94 ± 413.39</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>40.80 ± 61.75</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>416.95 ± 398.12</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>31.25 ± 89.41</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>521.04 ± 395.90</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>28.81 ± 47.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>483.01 ± 422.18</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>17.23 ± 43.73</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>530.88 ± 399.11</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>29.44 ± 54.99</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>429.69 ± 379.70</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>21.34 ± 60.95</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>511.87 ± 409.35</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20.13 ± 40.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>456.06 ± 415.16</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>19.45 ± 64.85</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>479.95 ± 404.55</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>31.16 ± 62.46</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>418.17 ± 398.98</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>24.90 ± 74.26</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>481.66 ± 406.59</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>24.06 ± 46.86</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Constraint Adapter Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>274.22 ± 206.70</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.73 ± 5.35</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>331.77 ± 194.50</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>42.47 ± 39.04</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>382.51 ± 194.85</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>21.93 ± 51.78</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>313.51 ± 200.44</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>30.90 ± 32.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>310.72 ± 207.58</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3.87 ± 13.05</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>372.30 ± 194.64</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>49.27 ± 45.39</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>414.22 ± 178.40</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>26.41 ± 65.00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>356.43 ± 196.31</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>37.44 ± 35.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>255.08 ± 205.78</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3.44 ± 7.76</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>280.15 ± 194.78</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>24.82 ± 25.13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>285.61 ± 220.89</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>15.26 ± 34.81</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>303.60 ± 191.87</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>21.21 ± 19.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>308.24 ± 209.05</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2.64 ± 4.19</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>329.59 ± 207.54</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>27.80 ± 24.35</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>382.04 ± 199.73</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>18.92 ± 39.25</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>352.27 ± 190.46</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>27.13 ± 24.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>306.30 ± 190.99</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.06 ± 5.41</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>344.78 ± 179.09</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>22.54 ± 22.43</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>368.84 ± 206.59</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12.39 ± 33.71</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>308.63 ± 200.17</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>16.47 ± 15.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>379.58 ± 182.91</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.37 ± 5.94</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>325.90 ± 190.72</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20.91 ± 20.75</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>388.51 ± 193.80</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>13.51 ± 50.33</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>378.63 ± 172.81</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>23.32 ± 24.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>305.69 ± 204.47</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>2.85 ± 7.56</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>330.75 ± 195.66</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>31.30 ± 32.73</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>370.29 ± 203.48</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>18.07 ± 47.39</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>335.51 ± 194.31</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>26.08 ± 27.10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Constraint Adapter Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>336.43 ± 469.09</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.60</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>479.65 ± 458.40</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>51.45 ± 64.03</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>415.31 ± 471.67</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.28 ± 1.29</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>539.25 ± 484.11</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>58.65 ± 83.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>322.81 ± 416.19</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.41 ± 2.93</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>514.14 ± 456.89</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>45.83 ± 60.33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>461.20 ± 461.15</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.71</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>574.30 ± 468.49</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>55.50 ± 74.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>307.20 ± 374.41</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>524.56 ± 450.77</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>34.89 ± 43.86</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>452.28 ± 452.05</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>682.20 ± 477.29</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>44.64 ± 58.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>290.74 ± 315.45</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.31</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>652.62 ± 445.76</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30.20 ± 28.88</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>539.21 ± 457.91</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.40 ± 2.84</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>610.53 ± 480.13</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>25.99 ± 33.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>308.55 ± 318.13</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>676.05 ± 459.13</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>26.17 ± 35.17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>569.64 ± 480.73</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.15 ± 0.90</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>743.36 ± 465.78</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>30.57 ± 46.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>313.15 ± 383.50</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0.12 ± 1.36</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>569.40 ± 461.08</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>37.71 ± 49.37</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>487.53 ± 468.37</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>0.19 ± 1.49</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>629.93 ± 480.92</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>43.07 ± 63.30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Constraint Adapter Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>503.97 ± 372.88</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.90 ± 6.84</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>574.27 ± 326.35</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>22.10 ± 35.26</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>543.63 ± 355.86</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>11.35 ± 59.01</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>567.69 ± 334.38</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>38.02 ± 88.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>497.70 ± 372.35</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>16.94 ± 56.17</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>532.74 ± 336.00</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15.01 ± 23.24</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>590.85 ± 325.32</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>21.14 ± 93.31</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>566.25 ± 336.28</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20.49 ± 35.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>455.71 ± 382.63</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>13.63 ± 48.76</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>529.19 ± 334.92</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18.25 ± 36.42</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>548.87 ± 355.81</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>12.24 ± 32.24</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>522.48 ± 337.11</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>19.71 ± 59.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>444.31 ± 373.95</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6.23 ± 21.24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>490.06 ± 331.14</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12.23 ± 18.51</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>544.92 ± 352.18</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5.41 ± 15.58</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>523.07 ± 329.72</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>19.36 ± 47.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>450.37 ± 373.13</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6.76 ± 20.02</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>530.27 ± 327.03</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14.64 ± 36.01</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>518.06 ± 355.14</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4.06 ± 10.78</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>580.81 ± 303.03</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>17.87 ± 52.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>470.41 ± 375.85</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>9.29 ± 36.24</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>531.31 ± 332.19</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>16.45 ± 31.01</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>549.27 ± 349.85</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>10.84 ± 52.48</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>552.06 ± 329.26</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>23.09 ± 60.07</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7860,4 +11120,502 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Goal Adapter Only</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Constraint Adapter Only</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Constraint Adapter Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>119.21 ± 112.80</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>128.23 ± 109.68</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8.28 ± 10.23</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>118.38 ± 112.45</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.28</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>119.83 ± 108.14</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4.94 ± 8.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>105.25 ± 116.54</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>123.40 ± 110.14</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7.61 ± 8.93</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>115.99 ± 110.67</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.42</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>123.30 ± 104.43</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>6.28 ± 8.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>113.72 ± 114.94</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>140.13 ± 105.32</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9.57 ± 13.59</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>129.74 ± 119.35</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.24</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>132.29 ± 107.67</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6.55 ± 8.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>127.26 ± 113.05</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>129.45 ± 112.93</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10.22 ± 17.76</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>126.06 ± 113.85</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.26</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>151.97 ± 113.07</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>7.00 ± 10.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>107.52 ± 110.99</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>144.36 ± 106.28</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11.36 ± 13.24</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>105.32 ± 111.33</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.63</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>150.30 ± 110.98</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>8.25 ± 14.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>114.59 ± 113.96</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.11</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>133.11 ± 109.19</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>9.41 ± 13.18</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>119.10 ± 113.89</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.39</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>135.54 ± 109.72</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>6.60 ± 10.34</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>